--- a/Car_Sales_Data(final project excel).xlsx
+++ b/Car_Sales_Data(final project excel).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\OneDrive - Future University in Egypt\Documents\Software_Engineering _2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99EB6E22-8399-4335-BB06-3A00B0B70EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1060A9C6-980D-4E4E-AA35-C1C386AE6EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="2" xr2:uid="{F6FEAB88-F3C7-4419-9DA7-703567157EBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{F6FEAB88-F3C7-4419-9DA7-703567157EBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Car_Sales_Data(1)" sheetId="1" r:id="rId1"/>
@@ -30,13 +30,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlcn.WorksheetConnection_KPIsC9C101" hidden="1">KPIs!$C$9:$C$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Dashboard(2)'!$A$1:$BE$67</definedName>
     <definedName name="Slicer_Brand">#N/A</definedName>
     <definedName name="Slicer_State">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="32" r:id="rId15"/>
-    <pivotCache cacheId="15" r:id="rId16"/>
+    <pivotCache cacheId="5" r:id="rId15"/>
+    <pivotCache cacheId="6" r:id="rId16"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -382,9 +383,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -515,6 +516,23 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color indexed="17"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="28"/>
+      <color indexed="17"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -865,9 +883,8 @@
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -876,6 +893,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -922,201 +940,714 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="77">
+  <dxfs count="238">
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -1145,41 +1676,11 @@
         <horizontal/>
       </border>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Car Sales" pivot="0" table="0" count="10" xr9:uid="{4F108BFD-AA8B-4ABB-9C8E-AA5EAD2A46BF}">
-      <tableStyleElement type="wholeTable" dxfId="66"/>
-      <tableStyleElement type="headerRow" dxfId="65"/>
+      <tableStyleElement type="wholeTable" dxfId="237"/>
+      <tableStyleElement type="headerRow" dxfId="236"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -1691,7 +2192,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -2047,6 +2550,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2054,7 +2558,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2481,7 +2984,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -2760,6 +3265,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2767,7 +3273,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3295,6 +3800,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3302,7 +3808,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3800,6 +4305,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3807,7 +4313,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4332,6 +4837,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4339,7 +4845,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4769,6 +5274,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4776,7 +5282,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5188,6 +5693,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5195,7 +5701,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5466,6 +5971,11 @@
             </a:effectLst>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="33"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+          </c:dPt>
           <c:cat>
             <c:strRef>
               <c:f>'Sales by Year'!$B$4:$B$38</c:f>
@@ -5815,6 +6325,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5822,7 +6333,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6321,6 +6831,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6328,7 +6839,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6926,6 +7436,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6933,7 +7444,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7382,6 +7892,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7389,7 +7900,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7701,7 +8211,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -8018,6 +8530,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8025,7 +8538,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8467,6 +8979,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8474,7 +8987,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8779,7 +9291,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -8816,8 +9330,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.9247594050743655E-2"/>
-          <c:y val="0.14087078651685395"/>
+          <c:x val="7.379300850071141E-2"/>
+          <c:y val="0.14896325405485228"/>
           <c:w val="0.90297462817147855"/>
           <c:h val="0.54922808104043175"/>
         </c:manualLayout>
@@ -9133,6 +9647,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9140,7 +9655,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9428,7 +9942,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -9465,8 +9981,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.14756528558077581"/>
-          <c:y val="0.17171296296296298"/>
+          <c:x val="0.14890666835659624"/>
+          <c:y val="0.17171280552826687"/>
           <c:w val="0.82969710641558614"/>
           <c:h val="0.58158792650918634"/>
         </c:manualLayout>
@@ -9706,6 +10222,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9713,7 +10230,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10075,7 +10591,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -10321,6 +10839,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10328,7 +10847,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10777,7 +11295,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -11206,6 +11726,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11213,7 +11734,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11669,7 +12189,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -11986,6 +12508,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11993,7 +12516,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12076,7 +12598,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="2160" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1680" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -12114,7 +12636,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="2160" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1680" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -12426,7 +12948,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -12775,7 +13297,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -12820,7 +13342,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -12849,6 +13371,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -12856,7 +13379,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12887,7 +13409,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr sz="1800"/>
+        <a:defRPr sz="1400"/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -13282,7 +13804,9 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -13563,6 +14087,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -13570,7 +14095,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -24548,6 +25072,14 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -24558,10 +25090,10 @@
       <xdr:rowOff>32657</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>10886</xdr:rowOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -24577,7 +25109,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10886" y="32657"/>
-          <a:ext cx="15914914" cy="12006943"/>
+          <a:ext cx="24220714" cy="8514443"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24623,10 +25155,10 @@
       <xdr:rowOff>60961</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>65313</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>54430</xdr:rowOff>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>86381</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -24642,9 +25174,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="1327390" y="60961"/>
-          <a:ext cx="14587523" cy="11837126"/>
+          <a:ext cx="23805910" cy="10160020"/>
           <a:chOff x="1327391" y="0"/>
-          <a:chExt cx="14260953" cy="12718143"/>
+          <a:chExt cx="14260953" cy="12404945"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
@@ -24661,7 +25193,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="1327391" y="0"/>
-            <a:ext cx="14260953" cy="12718143"/>
+            <a:ext cx="14260953" cy="10299184"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
             <a:avLst>
@@ -24869,10 +25401,10 @@
       <xdr:rowOff>163287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>249708</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>119744</xdr:rowOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -24888,7 +25420,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="1458689" y="163287"/>
-          <a:ext cx="14031019" cy="2917371"/>
+          <a:ext cx="21985511" cy="2503713"/>
           <a:chOff x="1491346" y="32659"/>
           <a:chExt cx="14031019" cy="2917371"/>
         </a:xfrm>
@@ -24972,8 +25504,8 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+          <mc:Choice Requires="a14">
             <xdr:graphicFrame macro="">
               <xdr:nvGraphicFramePr>
                 <xdr:cNvPr id="19" name="Brand 1">
@@ -24996,7 +25528,7 @@
               </a:graphic>
             </xdr:graphicFrame>
           </mc:Choice>
-          <mc:Fallback>
+          <mc:Fallback xmlns="">
             <xdr:sp macro="" textlink="">
               <xdr:nvSpPr>
                 <xdr:cNvPr id="0" name=""/>
@@ -25006,8 +25538,8 @@
               </xdr:nvSpPr>
               <xdr:spPr>
                 <a:xfrm>
-                  <a:off x="1618343" y="314053"/>
-                  <a:ext cx="2247900" cy="2624787"/>
+                  <a:off x="1708854" y="292675"/>
+                  <a:ext cx="3522284" cy="2252615"/>
                 </a:xfrm>
                 <a:prstGeom prst="rect">
                   <a:avLst/>
@@ -25115,8 +25647,8 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+          <mc:Choice Requires="a14">
             <xdr:graphicFrame macro="">
               <xdr:nvGraphicFramePr>
                 <xdr:cNvPr id="21" name="State 1">
@@ -25139,7 +25671,7 @@
               </a:graphic>
             </xdr:graphicFrame>
           </mc:Choice>
-          <mc:Fallback>
+          <mc:Fallback xmlns="">
             <xdr:sp macro="" textlink="">
               <xdr:nvSpPr>
                 <xdr:cNvPr id="0" name=""/>
@@ -25149,8 +25681,8 @@
               </xdr:nvSpPr>
               <xdr:spPr>
                 <a:xfrm>
-                  <a:off x="12934043" y="314054"/>
-                  <a:ext cx="2463800" cy="2480143"/>
+                  <a:off x="19439673" y="292676"/>
+                  <a:ext cx="3860582" cy="2128480"/>
                 </a:xfrm>
                 <a:prstGeom prst="rect">
                   <a:avLst/>
@@ -26539,15 +27071,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>206828</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>32658</xdr:rowOff>
+      <xdr:colOff>257628</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>144236</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>402771</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>119744</xdr:rowOff>
+      <xdr:colOff>453571</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>149678</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -26577,15 +27109,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>32657</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>65315</xdr:rowOff>
+      <xdr:colOff>337457</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>128815</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>174171</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>163287</xdr:rowOff>
+      <xdr:colOff>478971</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -26615,15 +27147,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>399928</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>64225</xdr:rowOff>
+      <xdr:colOff>545978</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>51525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>95128</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>9796</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -26652,16 +27184,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>227178</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>64225</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>292100</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>45175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>455778</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>9796</xdr:rowOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -26690,16 +27222,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>587828</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>64225</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>169545</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>174171</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>9796</xdr:rowOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>124370</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -26726,6 +27258,74 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>33</xdr:col>
+          <xdr:colOff>510540</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>38</xdr:col>
+          <xdr:colOff>175260</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>175260</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1025" name="Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1025"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="36576" bIns="32004" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="008000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:rPr>
+                <a:t>Clear Filters from Slices </a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
@@ -26862,10 +27462,10 @@
       <xdr:rowOff>32657</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>43543</xdr:rowOff>
+      <xdr:col>57</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -26881,7 +27481,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10886" y="32657"/>
-          <a:ext cx="18531114" cy="12279086"/>
+          <a:ext cx="34831564" cy="12540343"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -26921,16 +27521,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>108191</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>177800</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>12337</xdr:rowOff>
+      <xdr:col>58</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>133349</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -26945,9 +27545,9 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1327391" y="60960"/>
-          <a:ext cx="17138409" cy="12720320"/>
-          <a:chOff x="1327391" y="0"/>
+          <a:off x="1165860" y="0"/>
+          <a:ext cx="34597340" cy="12203429"/>
+          <a:chOff x="1296284" y="0"/>
           <a:chExt cx="14260953" cy="12718143"/>
         </a:xfrm>
       </xdr:grpSpPr>
@@ -26964,7 +27564,7 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="1327391" y="0"/>
+            <a:off x="1296284" y="0"/>
             <a:ext cx="14260953" cy="12718143"/>
           </a:xfrm>
           <a:prstGeom prst="roundRect">
@@ -27004,7 +27604,34 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="l"/>
-            <a:endParaRPr lang="en-US" sz="1100"/>
+            <a:endParaRPr lang="en-US" sz="1100" b="1" cap="none" spc="0">
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:pattFill prst="narHorz">
+                <a:fgClr>
+                  <a:schemeClr val="accent3"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="40000"/>
+                    <a:lumOff val="60000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:effectLst>
+                <a:innerShdw blurRad="177800">
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:innerShdw>
+              </a:effectLst>
+            </a:endParaRPr>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
@@ -27051,7 +27678,34 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="l"/>
-            <a:endParaRPr lang="en-US" sz="1100"/>
+            <a:endParaRPr lang="en-US" sz="1100" b="1" cap="none" spc="0">
+              <a:ln w="12700">
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:pattFill prst="narHorz">
+                <a:fgClr>
+                  <a:schemeClr val="accent3"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="40000"/>
+                    <a:lumOff val="60000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:effectLst>
+                <a:innerShdw blurRad="177800">
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:innerShdw>
+              </a:effectLst>
+            </a:endParaRPr>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
@@ -27168,15 +27822,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>239489</xdr:colOff>
+      <xdr:colOff>220439</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>163287</xdr:rowOff>
+      <xdr:rowOff>106137</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>249708</xdr:colOff>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>119744</xdr:rowOff>
+      <xdr:rowOff>62594</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -27191,8 +27845,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1458689" y="163287"/>
-          <a:ext cx="14031019" cy="2917371"/>
+          <a:off x="1439639" y="106137"/>
+          <a:ext cx="26449561" cy="2882537"/>
           <a:chOff x="1491346" y="32659"/>
           <a:chExt cx="14031019" cy="2917371"/>
         </a:xfrm>
@@ -27310,8 +27964,8 @@
               </xdr:nvSpPr>
               <xdr:spPr>
                 <a:xfrm>
-                  <a:off x="1618343" y="314053"/>
-                  <a:ext cx="2247900" cy="2624787"/>
+                  <a:off x="1740599" y="255102"/>
+                  <a:ext cx="4237466" cy="2593446"/>
                 </a:xfrm>
                 <a:prstGeom prst="rect">
                   <a:avLst/>
@@ -27453,8 +28107,8 @@
               </xdr:nvSpPr>
               <xdr:spPr>
                 <a:xfrm>
-                  <a:off x="12934043" y="314054"/>
-                  <a:ext cx="2463800" cy="2480143"/>
+                  <a:off x="23071573" y="255103"/>
+                  <a:ext cx="4644454" cy="2450529"/>
                 </a:xfrm>
                 <a:prstGeom prst="rect">
                   <a:avLst/>
@@ -28842,16 +29496,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>252242</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>71120</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>5080</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -28881,15 +29535,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>81279</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>71120</xdr:rowOff>
+      <xdr:colOff>396240</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>538479</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>5080</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>377190</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -28918,16 +29572,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>305888</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>170722</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>50618</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>160562</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>123008</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>119922</xdr:rowOff>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>123190</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -28957,15 +29611,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>346528</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>5622</xdr:rowOff>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>62772</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>132622</xdr:rowOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -28994,16 +29648,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>328748</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>132622</xdr:rowOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>99602</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>145868</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>81822</xdr:rowOff>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -29030,6 +29684,136 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>217077</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>43381</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>348854</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>63520</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="Rectangle 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6736565-8B99-654F-5116-706848DA0721}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1436277" y="2710381"/>
+          <a:ext cx="22686977" cy="7449639"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent6"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>38</xdr:col>
+          <xdr:colOff>198120</xdr:colOff>
+          <xdr:row>38</xdr:row>
+          <xdr:rowOff>133350</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>44</xdr:col>
+          <xdr:colOff>544830</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>57150</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2049" name="Button 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2049"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="32004" rIns="36576" bIns="32004" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="2800" b="1" i="1" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="008000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Aptos Narrow"/>
+                </a:rPr>
+                <a:t>Clear Slicer Filters  </a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
@@ -29207,8 +29991,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="Brand">
@@ -29231,7 +30015,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -29367,8 +30151,8 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="State">
@@ -29391,7 +30175,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -33217,45 +34001,137 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB64DFF3-28E9-4AB7-81CE-B9A8A5DB5CB1}" name="PivotTable4" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C9:C10" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="1">
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{25069415-C28E-47A8-9071-DA4F557F28BA}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B2:E3" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="13">
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
   <rowItems count="1">
     <i/>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
   </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Distinict count of Brand" fld="0" baseField="0" baseItem="0"/>
+  <dataFields count="4">
+    <dataField name="Sum of Total Sales" fld="10" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Sum of Quantity" fld="9" baseField="0" baseItem="0"/>
+    <dataField name="Count of Brand" fld="2" subtotal="count" baseField="0" baseItem="1"/>
+    <dataField name="Average of Unit Price" fld="8" subtotal="average" baseField="0" baseItem="1" numFmtId="164"/>
   </dataFields>
-  <pivotHierarchies count="4">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
+  <formats count="3">
+    <format dxfId="234">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="233">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="232">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_KPIs!$C$9:$C$10">
-        <x15:activeTabTopLevelEntity name="[Range]"/>
-      </x15:pivotTableUISettings>
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+      <xpdl:pivotTableDefinition16/>
     </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4507C62-9137-44BC-AEF8-219CA262E1CF}" name="PivotTable12" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4507C62-9137-44BC-AEF8-219CA262E1CF}" name="PivotTable12" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="B3:C38" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField numFmtId="14" showAll="0">
@@ -33514,7 +34390,7 @@
     <dataField name="Average of Condition" fld="5" subtotal="average" baseField="1" baseItem="0" numFmtId="2"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="62">
+    <format dxfId="223">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -33551,7 +34427,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9BB62EF0-B0F5-4687-A3C6-696CDBD3C6F5}" name="PivotTable13" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9BB62EF0-B0F5-4687-A3C6-696CDBD3C6F5}" name="PivotTable13" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="20">
   <location ref="B3:C13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField numFmtId="14" showAll="0">
@@ -33751,7 +34627,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FDFEE903-625D-4FE5-AC46-90DB3D8BF9A0}" name="PivotTable14" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FDFEE903-625D-4FE5-AC46-90DB3D8BF9A0}" name="PivotTable14" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="B3:C15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField axis="axisRow" numFmtId="14" showAll="0">
@@ -33885,13 +34761,13 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="10" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Sum of Total Sales" fld="10" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="61">
+    <format dxfId="222">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="60">
+    <format dxfId="221">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -33946,137 +34822,45 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{25069415-C28E-47A8-9071-DA4F557F28BA}" name="PivotTable1" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B2:E3" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="13">
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="14">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB64DFF3-28E9-4AB7-81CE-B9A8A5DB5CB1}" name="PivotTable4" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C9:C10" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="1">
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowItems count="1">
     <i/>
   </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
-  <dataFields count="4">
-    <dataField name="Sum of Total Sales" fld="10" baseField="0" baseItem="0" numFmtId="165"/>
-    <dataField name="Sum of Quantity" fld="9" baseField="0" baseItem="0"/>
-    <dataField name="Count of Brand" fld="2" subtotal="count" baseField="0" baseItem="1"/>
-    <dataField name="Average of Unit Price" fld="8" subtotal="average" baseField="0" baseItem="1" numFmtId="165"/>
+  <dataFields count="1">
+    <dataField name="Sum of Distinict count of Brand" fld="0" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="3">
-    <format dxfId="75">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="74">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="73">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
+  <pivotHierarchies count="4">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_KPIs!$C$9:$C$10">
+        <x15:activeTabTopLevelEntity name="[Range]"/>
+      </x15:pivotTableUISettings>
     </ext>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
     </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B246B650-FE08-4549-A85F-CB1D0F76DCCE}" name="PivotTable5" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B246B650-FE08-4549-A85F-CB1D0F76DCCE}" name="PivotTable5" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
   <location ref="B2:C25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField numFmtId="14" showAll="0">
@@ -34266,13 +35050,13 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="10" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Sum of Total Sales" fld="10" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="72">
+    <format dxfId="231">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="71">
+    <format dxfId="230">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -34309,7 +35093,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{121616F0-3370-4D2D-84F4-C165B2218500}" name="PivotTable6" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{121616F0-3370-4D2D-84F4-C165B2218500}" name="PivotTable6" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
   <location ref="B2:C12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField numFmtId="14" showAll="0">
@@ -34446,13 +35230,13 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Average of Total Sales" fld="10" subtotal="average" baseField="2" baseItem="0" numFmtId="165"/>
+    <dataField name="Average of Total Sales" fld="10" subtotal="average" baseField="2" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="70">
+    <format dxfId="229">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="69">
+    <format dxfId="228">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -34498,7 +35282,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DC088DFC-FA69-4F31-B945-EF6FFE4EFA2F}" name="PivotTable7" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DC088DFC-FA69-4F31-B945-EF6FFE4EFA2F}" name="PivotTable7" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="B2:C25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField numFmtId="14" showAll="0">
@@ -34735,7 +35519,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0EEC2B9E-5FEB-4032-8B10-9DD2097C8730}" name="PivotTable8" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="54">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0EEC2B9E-5FEB-4032-8B10-9DD2097C8730}" name="PivotTable8" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="54">
   <location ref="B3:C13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField numFmtId="14" showAll="0">
@@ -34886,13 +35670,13 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="10" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Sum of Total Sales" fld="10" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="68">
+    <format dxfId="227">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="67">
+    <format dxfId="226">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -34929,7 +35713,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F9FC32FE-6A9F-4BA5-96A9-AD116C2A04CB}" name="PivotTable9" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F9FC32FE-6A9F-4BA5-96A9-AD116C2A04CB}" name="PivotTable9" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
   <location ref="B2:C4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField numFmtId="14" showAll="0">
@@ -35136,7 +35920,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C7FD1668-B2B8-434E-8DC0-6893F7EB1F8F}" name="PivotTable10" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C7FD1668-B2B8-434E-8DC0-6893F7EB1F8F}" name="PivotTable10" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="B3:C38" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField numFmtId="14" showAll="0">
@@ -35392,13 +36176,13 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="10" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Sum of Total Sales" fld="10" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="64">
+    <format dxfId="225">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="63">
+    <format dxfId="224">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -35447,7 +36231,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{84EC58D9-0084-4B3C-9841-D3D8128A85AD}" name="PivotTable11" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{84EC58D9-0084-4B3C-9841-D3D8128A85AD}" name="PivotTable11" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
   <location ref="B3:C13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField numFmtId="14" showAll="0">
@@ -35769,7 +36553,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FF3DB1C7-0A8C-45D2-A047-306277231A20}" name="Table1" displayName="Table1" ref="A1:K251" totalsRowShown="0">
   <autoFilter ref="A1:K251" xr:uid="{FF3DB1C7-0A8C-45D2-A047-306277231A20}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{2D556FF4-14E3-40D9-87D6-43CB2295B150}" name="Date" dataDxfId="76"/>
+    <tableColumn id="1" xr3:uid="{2D556FF4-14E3-40D9-87D6-43CB2295B150}" name="Date" dataDxfId="235"/>
     <tableColumn id="2" xr3:uid="{A4039974-1528-463E-A2FD-6F6F3AF87B88}" name="Year"/>
     <tableColumn id="3" xr3:uid="{ADC6E122-6652-49C5-A010-FD902F8D6084}" name="Brand"/>
     <tableColumn id="4" xr3:uid="{02B66A37-8557-4DF8-B3A5-061F783168F3}" name="State"/>
@@ -36102,6 +36886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF965CF9-4F89-45F1-86FB-CB2CCD2784F7}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K251"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -44909,6 +45694,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA0C783B-E3CA-42CC-B7AA-E57A79B9805E}">
+  <sheetPr codeName="Sheet10"/>
   <dimension ref="B3:C38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -44917,290 +45703,290 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>1990</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>1383000</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>1991</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>2134000</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>1992</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>302000</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>1993</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>804000</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>1994</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>1236000</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>1995</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>896000</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>1996</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>1415000</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>1997</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>1596000</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>1998</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>1161000</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>1999</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>337000</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <v>2000</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
         <v>1200000</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>2001</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="3">
         <v>1287000</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <v>2002</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="3">
         <v>1211000</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="6">
+      <c r="B17" s="5">
         <v>2003</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="3">
         <v>3707000</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="6">
+      <c r="B18" s="5">
         <v>2004</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="3">
         <v>932000</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="6">
+      <c r="B19" s="5">
         <v>2005</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="3">
         <v>300000</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" s="6">
+      <c r="B20" s="5">
         <v>2006</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="3">
         <v>1811000</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" s="6">
+      <c r="B21" s="5">
         <v>2007</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="3">
         <v>945000</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B22" s="6">
+      <c r="B22" s="5">
         <v>2008</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="3">
         <v>1992000</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>2009</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="3">
         <v>2199000</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B24" s="6">
+      <c r="B24" s="5">
         <v>2010</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="3">
         <v>2585000</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B25" s="6">
+      <c r="B25" s="5">
         <v>2011</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="3">
         <v>2967000</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B26" s="6">
+      <c r="B26" s="5">
         <v>2012</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="3">
         <v>2080000</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B27" s="6">
+      <c r="B27" s="5">
         <v>2013</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="3">
         <v>1461000</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B28" s="6">
+      <c r="B28" s="5">
         <v>2014</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="3">
         <v>2130000</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B29" s="6">
+      <c r="B29" s="5">
         <v>2015</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="3">
         <v>656000</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B30" s="6">
+      <c r="B30" s="5">
         <v>2016</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="3">
         <v>613000</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B31" s="6">
+      <c r="B31" s="5">
         <v>2017</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="3">
         <v>950000</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B32" s="6">
+      <c r="B32" s="5">
         <v>2018</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="3">
         <v>2570000</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B33" s="6">
+      <c r="B33" s="5">
         <v>2019</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="3">
         <v>459000</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B34" s="6">
+      <c r="B34" s="5">
         <v>2020</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="3">
         <v>1137000</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B35" s="6">
+      <c r="B35" s="5">
         <v>2021</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="3">
         <v>830000</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B36" s="6">
+      <c r="B36" s="5">
         <v>2022</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="3">
         <v>840000</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B37" s="6">
+      <c r="B37" s="5">
         <v>2023</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="3">
         <v>1806000</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B38" s="6">
+      <c r="B38" s="5">
         <v>2024</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="3">
         <v>170000</v>
       </c>
     </row>
@@ -45219,6 +46005,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD18065-2C9F-4AD3-808A-0CE8A251DCAA}">
+  <sheetPr codeName="Sheet11"/>
   <dimension ref="B3:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -45227,7 +46014,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C3" t="s">
@@ -45235,82 +46022,82 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="8">
         <v>68</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="8">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="8">
         <v>66</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="8">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="8">
         <v>49</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="8">
         <v>45</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="8">
         <v>45</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="8">
         <v>44</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="8">
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="8">
         <v>39</v>
       </c>
     </row>
@@ -45322,6 +46109,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A2D4B13-62E6-4D4D-84A7-3FCE7E4503BE}">
+  <sheetPr codeName="Sheet12"/>
   <dimension ref="B3:C38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -45330,7 +46118,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C3" t="s">
@@ -45338,282 +46126,282 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>1990</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>5.1375000000000002</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>1991</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>5.866666666666668</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>1992</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>7.5750000000000002</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>1993</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>7.625</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>1994</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>10.059999999999999</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>1995</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>11.5</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>1996</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>11.718181818181819</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>1997</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>12.9625</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>1998</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>13.366666666666667</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>1999</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>12.966666666666667</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <v>2000</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <v>15.580000000000002</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>2001</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="6">
         <v>16.79</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <v>2002</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="6">
         <v>17.32</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="6">
+      <c r="B17" s="5">
         <v>2003</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>18.108333333333334</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="6">
+      <c r="B18" s="5">
         <v>2004</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="6">
         <v>19.475000000000001</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="6">
+      <c r="B19" s="5">
         <v>2005</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="6">
         <v>22.700000000000003</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" s="6">
+      <c r="B20" s="5">
         <v>2006</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="6">
         <v>21.472727272727273</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" s="6">
+      <c r="B21" s="5">
         <v>2007</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="6">
         <v>21.771428571428569</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B22" s="6">
+      <c r="B22" s="5">
         <v>2008</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="6">
         <v>23.988888888888891</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>2009</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="6">
         <v>24.990909090909089</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B24" s="6">
+      <c r="B24" s="5">
         <v>2010</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="6">
         <v>26.153846153846157</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B25" s="6">
+      <c r="B25" s="5">
         <v>2011</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="6">
         <v>27.138461538461538</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B26" s="6">
+      <c r="B26" s="5">
         <v>2012</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="6">
         <v>27.266666666666666</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B27" s="6">
+      <c r="B27" s="5">
         <v>2013</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="6">
         <v>28.8</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B28" s="6">
+      <c r="B28" s="5">
         <v>2014</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="6">
         <v>30.111111111111111</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B29" s="6">
+      <c r="B29" s="5">
         <v>2015</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="6">
         <v>31.166666666666671</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B30" s="6">
+      <c r="B30" s="5">
         <v>2016</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="6">
         <v>29.98</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B31" s="6">
+      <c r="B31" s="5">
         <v>2017</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="6">
         <v>32.019999999999996</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B32" s="6">
+      <c r="B32" s="5">
         <v>2018</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="6">
         <v>33.636363636363633</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B33" s="6">
+      <c r="B33" s="5">
         <v>2019</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="6">
         <v>35.216666666666669</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B34" s="6">
+      <c r="B34" s="5">
         <v>2020</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="6">
         <v>36.866666666666667</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B35" s="6">
+      <c r="B35" s="5">
         <v>2021</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="6">
         <v>35.114285714285714</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B36" s="6">
+      <c r="B36" s="5">
         <v>2022</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="6">
         <v>38.700000000000003</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B37" s="6">
+      <c r="B37" s="5">
         <v>2023</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="6">
         <v>38.577777777777776</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B38" s="6">
+      <c r="B38" s="5">
         <v>2024</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="6">
         <v>39.200000000000003</v>
       </c>
     </row>
@@ -45625,6 +46413,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{651583CD-305F-4077-AC5A-759BED9F6692}">
+  <sheetPr codeName="Sheet13"/>
   <dimension ref="B3:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -45633,7 +46422,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C3" t="s">
@@ -45641,82 +46430,82 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="8">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="8">
         <v>97</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="8">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="8">
         <v>82</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="8">
         <v>79</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="8">
         <v>73</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="8">
         <v>72</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="8">
         <v>66</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="8">
         <v>65</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="8">
         <v>60</v>
       </c>
     </row>
@@ -45728,114 +46517,115 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D7AF627-65D0-4F5E-8DC6-22AA922B42DF}">
+  <sheetPr codeName="Sheet14"/>
   <dimension ref="B3:C15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>4985000</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>3738000</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>2687000</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>2938000</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>4901000</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>3326000</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>5312000</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>4190000</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>3740000</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>4871000</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
         <v>3220000</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="3">
         <v>4194000</v>
       </c>
     </row>
@@ -45846,16 +46636,47 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{550EC4E9-C4C8-412C-86E3-190FED543B08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{550EC4E9-C4C8-412C-86E3-190FED543B08}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1025" r:id="rId4" name="Button 1">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!SimpleClearFiltersAndSlicers">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>33</xdr:col>
+                    <xdr:colOff>510540</xdr:colOff>
+                    <xdr:row>33</xdr:row>
+                    <xdr:rowOff>15240</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>38</xdr:col>
+                    <xdr:colOff>175260</xdr:colOff>
+                    <xdr:row>44</xdr:row>
+                    <xdr:rowOff>175260</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
+        <x14:slicer r:id="rId5"/>
       </x14:slicerList>
     </ext>
   </extLst>
@@ -45863,16 +46684,47 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF6000B-BE14-4164-AA28-CFD1E442AB91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF6000B-BE14-4164-AA28-CFD1E442AB91}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2049" r:id="rId4" name="Button 1">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!SimpleClearFiltersAndSlicers">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>38</xdr:col>
+                    <xdr:colOff>198120</xdr:colOff>
+                    <xdr:row>38</xdr:row>
+                    <xdr:rowOff>137160</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>44</xdr:col>
+                    <xdr:colOff>548640</xdr:colOff>
+                    <xdr:row>53</xdr:row>
+                    <xdr:rowOff>60960</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
+        <x14:slicer r:id="rId5"/>
       </x14:slicerList>
     </ext>
   </extLst>
@@ -45881,17 +46733,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{932625BB-FB13-4C27-B1DF-A07F3A4B2D2F}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C2" t="s">
@@ -45905,16 +46758,16 @@
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>48102000</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3">
         <v>777</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3">
         <v>250</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>61384</v>
       </c>
     </row>
@@ -45924,7 +46777,7 @@
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C10" s="2">
+      <c r="C10">
         <v>23</v>
       </c>
     </row>
@@ -45935,202 +46788,203 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC6A3B39-6C48-4770-B3C4-DE308740F932}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:C25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>6880000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>6580000</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>5040000</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>4400000</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>2640000</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>2240000</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>1980000</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>1927000</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>1876000</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>1750000</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>1500000</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
         <v>1430000</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="3">
         <v>1421000</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="3">
         <v>1320000</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="3">
         <v>1092000</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="3">
         <v>1050000</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="3">
         <v>945000</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="3">
         <v>782000</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="3">
         <v>768000</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="3">
         <v>702000</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="3">
         <v>675000</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="3">
         <v>624000</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="3">
         <v>480000</v>
       </c>
     </row>
@@ -46143,98 +46997,99 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A066A8-C7A1-48D8-ACA9-5A4507CAAF08}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>560000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>529230.76923076925</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>470000</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>330000</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>275000</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>224000</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>204285.71428571429</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>188571.42857142858</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>159090.90909090909</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>152307.69230769231</v>
       </c>
     </row>
@@ -46246,6 +47101,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94FD9799-F160-4CE3-A09B-A1AFC74135E1}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="B2:C25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -46254,7 +47110,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C2" t="s">
@@ -46262,186 +47118,186 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="8">
         <v>67</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="8">
         <v>55</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="8">
         <v>49</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="8">
         <v>47</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="8">
         <v>43</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="8">
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="8">
         <v>41</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="8">
         <v>36</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="8">
         <v>35</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="8">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="8">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="8">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="8">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="8">
         <v>30</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="8">
         <v>28</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="8">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="8">
         <v>26</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="8">
         <v>26</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="8">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="8">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="8">
         <v>21</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="8">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="8">
         <v>12</v>
       </c>
     </row>
@@ -46453,6 +47309,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA39042A-923F-4FE2-A0F7-F47802604AC7}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="B3:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -46461,90 +47318,90 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>9737000</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>7342000</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>5865000</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>4625000</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>3981000</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>3768000</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>3587000</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>3538000</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>3154000</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>2505000</v>
       </c>
     </row>
@@ -46564,6 +47421,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{199F43E9-5D8A-4278-A685-C71F72E8F4A5}">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="B2:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -46572,7 +47430,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C2" t="s">
@@ -46580,18 +47438,18 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="8">
         <v>406</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="8">
         <v>371</v>
       </c>
     </row>
@@ -46602,6 +47460,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="038b4bb4-3b65-458f-ae0a-b691865ac3fd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -46610,7 +47476,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F8C7127295091E4C85CF87021765FEF0" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bcfd26a0f62c00857dafb459a3827f61">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="038b4bb4-3b65-458f-ae0a-b691865ac3fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbebaa01931f0fe46dabb39968d31881" ns3:_="">
     <xsd:import namespace="038b4bb4-3b65-458f-ae0a-b691865ac3fd"/>
@@ -46798,15 +47664,23 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="038b4bb4-3b65-458f-ae0a-b691865ac3fd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AD12F74-43FC-4DF3-9DBB-E2701AE468AE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="038b4bb4-3b65-458f-ae0a-b691865ac3fd"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24065C38-1615-4A02-A318-9B8493B4FC03}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -46814,7 +47688,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{286CE2A3-8178-4BC3-8CBB-A2810EDA34BF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -46830,20 +47704,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AD12F74-43FC-4DF3-9DBB-E2701AE468AE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="038b4bb4-3b65-458f-ae0a-b691865ac3fd"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>